--- a/data/2.0_balancing_selection/01_b2_candidates/W_L_I_5kb_description.xlsx
+++ b/data/2.0_balancing_selection/01_b2_candidates/W_L_I_5kb_description.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/2.0_balancing_selection/01_b2_candidates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886EE3E2-5EAC-DA41-95F5-E26372BFD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FE0A3A-0CA4-F747-91A2-B443204141CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27040" yWindow="-5200" windowWidth="51200" windowHeight="28180" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="332">
   <si>
     <t>V1</t>
   </si>
@@ -1028,6 +1028,15 @@
   </si>
   <si>
     <t>kinase(n=2)</t>
+  </si>
+  <si>
+    <t>#ff7f0</t>
+  </si>
+  <si>
+    <t>#33a02c</t>
+  </si>
+  <si>
+    <t>#1f78b</t>
   </si>
 </sst>
 </file>
@@ -1401,6 +1410,13 @@
   <dimension ref="A1:Y160"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="9" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="75.33203125" customWidth="1"/>
   </cols>
@@ -16698,13 +16714,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBEA331F-FAF3-FA4D-99BA-09633F6307B7}">
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="24" max="24" width="49.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16780,7 +16796,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -16859,8 +16875,11 @@
       <c r="Z2" s="4" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA2" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -16939,8 +16958,11 @@
       <c r="Z3" s="4" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA3" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -17019,8 +17041,11 @@
       <c r="Z4" s="4" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA4" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -17099,8 +17124,11 @@
       <c r="Z5" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA5" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -17179,342 +17207,357 @@
       <c r="Z6" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="AA6" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
         <v>2</v>
       </c>
-      <c r="B7">
-        <v>67161993</v>
-      </c>
-      <c r="C7">
-        <v>67206548</v>
-      </c>
-      <c r="D7">
-        <v>1152</v>
-      </c>
-      <c r="E7">
-        <v>2089.3892660000001</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="B7" s="4">
+        <v>3891951</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3904895</v>
+      </c>
+      <c r="D7" s="4">
+        <v>178</v>
+      </c>
+      <c r="E7" s="4">
+        <v>946.21085140000002</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="4">
         <v>2</v>
       </c>
-      <c r="H7">
-        <v>67156384</v>
-      </c>
-      <c r="I7">
-        <v>67240850</v>
-      </c>
-      <c r="J7">
-        <v>1572</v>
-      </c>
-      <c r="K7">
-        <v>2747.1696609999999</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="H7" s="4">
+        <v>3891951</v>
+      </c>
+      <c r="I7" s="4">
+        <v>3904496</v>
+      </c>
+      <c r="J7" s="4">
+        <v>132</v>
+      </c>
+      <c r="K7" s="4">
+        <v>1766.6600980000001</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="4">
         <v>2</v>
       </c>
-      <c r="N7">
-        <v>67161195</v>
-      </c>
-      <c r="O7">
-        <v>67212110</v>
-      </c>
-      <c r="P7">
-        <v>1046</v>
-      </c>
-      <c r="Q7">
-        <v>2405.171034</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="N7" s="4">
+        <v>3884986</v>
+      </c>
+      <c r="O7" s="4">
+        <v>3912663</v>
+      </c>
+      <c r="P7" s="4">
+        <v>559</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1783.198664</v>
+      </c>
+      <c r="R7" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="4">
         <v>2</v>
       </c>
-      <c r="T7">
-        <v>67197791</v>
-      </c>
-      <c r="U7">
-        <v>67208342</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="T7" s="4">
+        <v>3884552</v>
+      </c>
+      <c r="U7" s="4">
+        <v>3902872</v>
+      </c>
+      <c r="V7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="W7" t="s">
-        <v>67</v>
-      </c>
-      <c r="X7" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y7" t="s">
+      <c r="W7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4">
+        <v>4721370</v>
+      </c>
+      <c r="C8" s="4">
+        <v>4762544</v>
+      </c>
+      <c r="D8" s="4">
+        <v>971</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1913.770626</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="G8" s="4">
+        <v>3</v>
+      </c>
+      <c r="H8" s="4">
+        <v>4736814</v>
+      </c>
+      <c r="I8" s="4">
+        <v>4754328</v>
+      </c>
+      <c r="J8" s="4">
+        <v>283</v>
+      </c>
+      <c r="K8" s="4">
+        <v>1825.9663539999999</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="M8" s="4">
+        <v>3</v>
+      </c>
+      <c r="N8" s="4">
+        <v>4719612</v>
+      </c>
+      <c r="O8" s="4">
+        <v>4767808</v>
+      </c>
+      <c r="P8" s="4">
+        <v>1058</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>2654.4997600000002</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="S8" s="4">
+        <v>3</v>
+      </c>
+      <c r="T8" s="4">
+        <v>4730884</v>
+      </c>
+      <c r="U8" s="4">
+        <v>4739818</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y8" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="Z8" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>16833284</v>
-      </c>
-      <c r="C8">
-        <v>16906729</v>
-      </c>
-      <c r="D8">
-        <v>1489</v>
-      </c>
-      <c r="E8">
-        <v>1615.7541639999999</v>
-      </c>
-      <c r="F8" t="s">
-        <v>322</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-      <c r="H8">
-        <v>16876435</v>
-      </c>
-      <c r="I8">
-        <v>16889098</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>1832.3460869999999</v>
-      </c>
-      <c r="L8" t="s">
-        <v>324</v>
-      </c>
-      <c r="M8">
-        <v>2</v>
-      </c>
-      <c r="N8">
-        <v>16841388</v>
-      </c>
-      <c r="O8">
-        <v>16874528</v>
-      </c>
-      <c r="P8">
-        <v>844</v>
-      </c>
-      <c r="Q8">
-        <v>1882.994557</v>
-      </c>
-      <c r="R8" t="s">
-        <v>323</v>
-      </c>
-      <c r="S8">
-        <v>2</v>
-      </c>
-      <c r="T8">
-        <v>16858441</v>
-      </c>
-      <c r="U8">
-        <v>16871556</v>
-      </c>
-      <c r="V8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W8" t="s">
-        <v>46</v>
-      </c>
-      <c r="X8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>319</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA8" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="4">
-        <v>3891951</v>
+        <v>66577675</v>
       </c>
       <c r="C9" s="4">
-        <v>3904895</v>
+        <v>66660340</v>
       </c>
       <c r="D9" s="4">
-        <v>178</v>
+        <v>2148</v>
       </c>
       <c r="E9" s="4">
-        <v>946.21085140000002</v>
+        <v>2737.916577</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G9" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="4">
-        <v>3891951</v>
+        <v>66601679</v>
       </c>
       <c r="I9" s="4">
-        <v>3904496</v>
+        <v>66649218</v>
       </c>
       <c r="J9" s="4">
-        <v>132</v>
+        <v>1118</v>
       </c>
       <c r="K9" s="4">
-        <v>1766.6600980000001</v>
+        <v>2781.4364580000001</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M9" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" s="4">
-        <v>3884986</v>
+        <v>66582969</v>
       </c>
       <c r="O9" s="4">
-        <v>3912663</v>
+        <v>66662954</v>
       </c>
       <c r="P9" s="4">
-        <v>559</v>
+        <v>2272</v>
       </c>
       <c r="Q9" s="4">
-        <v>1783.198664</v>
+        <v>4193.4089190000004</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S9" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" s="4">
-        <v>3884552</v>
+        <v>66576387</v>
       </c>
       <c r="U9" s="4">
-        <v>3902872</v>
+        <v>66582986</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Z9" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>63052282</v>
-      </c>
-      <c r="C10">
-        <v>63092572</v>
-      </c>
-      <c r="D10">
-        <v>825</v>
-      </c>
-      <c r="E10">
-        <v>1521.3566880000001</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="AA9" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>3</v>
+      </c>
+      <c r="B10" s="4">
+        <v>66577675</v>
+      </c>
+      <c r="C10" s="4">
+        <v>66660340</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2148</v>
+      </c>
+      <c r="E10" s="4">
+        <v>2737.916577</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-      <c r="H10">
-        <v>63062915</v>
-      </c>
-      <c r="I10">
-        <v>63086509</v>
-      </c>
-      <c r="J10">
-        <v>423</v>
-      </c>
-      <c r="K10">
-        <v>1814.0876330000001</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="G10" s="4">
+        <v>3</v>
+      </c>
+      <c r="H10" s="4">
+        <v>66601679</v>
+      </c>
+      <c r="I10" s="4">
+        <v>66649218</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1118</v>
+      </c>
+      <c r="K10" s="4">
+        <v>2781.4364580000001</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="M10">
-        <v>3</v>
-      </c>
-      <c r="N10">
-        <v>63059302</v>
-      </c>
-      <c r="O10">
-        <v>63084877</v>
-      </c>
-      <c r="P10">
-        <v>541</v>
-      </c>
-      <c r="Q10">
-        <v>1370.5586989999999</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="M10" s="4">
+        <v>3</v>
+      </c>
+      <c r="N10" s="4">
+        <v>66582969</v>
+      </c>
+      <c r="O10" s="4">
+        <v>66662954</v>
+      </c>
+      <c r="P10" s="4">
+        <v>2272</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>4193.4089190000004</v>
+      </c>
+      <c r="R10" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="S10">
-        <v>3</v>
-      </c>
-      <c r="T10">
-        <v>63060671</v>
-      </c>
-      <c r="U10">
-        <v>63067137</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="S10" s="4">
+        <v>3</v>
+      </c>
+      <c r="T10" s="4">
+        <v>66594310</v>
+      </c>
+      <c r="U10" s="4">
+        <v>66602908</v>
+      </c>
+      <c r="V10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W10" t="s">
-        <v>88</v>
-      </c>
-      <c r="X10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="Z10" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="AA10" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>3</v>
       </c>
       <c r="B11" s="4">
-        <v>4721370</v>
+        <v>80160964</v>
       </c>
       <c r="C11" s="4">
-        <v>4762544</v>
+        <v>80183873</v>
       </c>
       <c r="D11" s="4">
-        <v>971</v>
+        <v>640</v>
       </c>
       <c r="E11" s="4">
-        <v>1913.770626</v>
+        <v>1191.1170669999999</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>322</v>
@@ -17523,16 +17566,16 @@
         <v>3</v>
       </c>
       <c r="H11" s="4">
-        <v>4736814</v>
+        <v>80165838</v>
       </c>
       <c r="I11" s="4">
-        <v>4754328</v>
+        <v>80178577</v>
       </c>
       <c r="J11" s="4">
-        <v>283</v>
+        <v>42</v>
       </c>
       <c r="K11" s="4">
-        <v>1825.9663539999999</v>
+        <v>1700.847135</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>324</v>
@@ -17541,16 +17584,16 @@
         <v>3</v>
       </c>
       <c r="N11" s="4">
-        <v>4719612</v>
+        <v>80161669</v>
       </c>
       <c r="O11" s="4">
-        <v>4767808</v>
+        <v>80189103</v>
       </c>
       <c r="P11" s="4">
-        <v>1058</v>
+        <v>615</v>
       </c>
       <c r="Q11" s="4">
-        <v>2654.4997600000002</v>
+        <v>1834.9834739999999</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>323</v>
@@ -17559,42 +17602,45 @@
         <v>3</v>
       </c>
       <c r="T11" s="4">
-        <v>4730884</v>
+        <v>80175492</v>
       </c>
       <c r="U11" s="4">
-        <v>4739818</v>
+        <v>80180787</v>
       </c>
       <c r="V11" s="4" t="s">
         <v>26</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+      <c r="AA11" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>3</v>
       </c>
       <c r="B12" s="4">
-        <v>66577675</v>
+        <v>63052282</v>
       </c>
       <c r="C12" s="4">
-        <v>66660340</v>
+        <v>63092572</v>
       </c>
       <c r="D12" s="4">
-        <v>2148</v>
+        <v>825</v>
       </c>
       <c r="E12" s="4">
-        <v>2737.916577</v>
+        <v>1521.3566880000001</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>322</v>
@@ -17603,16 +17649,16 @@
         <v>3</v>
       </c>
       <c r="H12" s="4">
-        <v>66601679</v>
+        <v>63062915</v>
       </c>
       <c r="I12" s="4">
-        <v>66649218</v>
+        <v>63086509</v>
       </c>
       <c r="J12" s="4">
-        <v>1118</v>
+        <v>423</v>
       </c>
       <c r="K12" s="4">
-        <v>2781.4364580000001</v>
+        <v>1814.0876330000001</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>324</v>
@@ -17621,16 +17667,16 @@
         <v>3</v>
       </c>
       <c r="N12" s="4">
-        <v>66582969</v>
+        <v>63059302</v>
       </c>
       <c r="O12" s="4">
-        <v>66662954</v>
+        <v>63084877</v>
       </c>
       <c r="P12" s="4">
-        <v>2272</v>
+        <v>541</v>
       </c>
       <c r="Q12" s="4">
-        <v>4193.4089190000004</v>
+        <v>1370.5586989999999</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>323</v>
@@ -17639,1790 +17685,531 @@
         <v>3</v>
       </c>
       <c r="T12" s="4">
-        <v>66576387</v>
+        <v>63085267</v>
       </c>
       <c r="U12" s="4">
-        <v>66582986</v>
+        <v>63097361</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="Z12" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA12" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B13" s="4">
-        <v>66577675</v>
+        <v>63994501</v>
       </c>
       <c r="C13" s="4">
-        <v>66660340</v>
+        <v>64034128</v>
       </c>
       <c r="D13" s="4">
-        <v>2148</v>
+        <v>1317</v>
       </c>
       <c r="E13" s="4">
-        <v>2737.916577</v>
+        <v>1293.8785130000001</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G13" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" s="4">
-        <v>66601679</v>
+        <v>63999374</v>
       </c>
       <c r="I13" s="4">
-        <v>66649218</v>
+        <v>64076061</v>
       </c>
       <c r="J13" s="4">
-        <v>1118</v>
+        <v>1294</v>
       </c>
       <c r="K13" s="4">
-        <v>2781.4364580000001</v>
+        <v>3430.8111159999999</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M13" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N13" s="4">
-        <v>66582969</v>
+        <v>63985680</v>
       </c>
       <c r="O13" s="4">
-        <v>66662954</v>
+        <v>64044018</v>
       </c>
       <c r="P13" s="4">
-        <v>2272</v>
+        <v>1458</v>
       </c>
       <c r="Q13" s="4">
-        <v>4193.4089190000004</v>
+        <v>2731.3774370000001</v>
       </c>
       <c r="R13" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S13" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" s="4">
-        <v>66594310</v>
+        <v>64009875</v>
       </c>
       <c r="U13" s="4">
-        <v>66602908</v>
+        <v>64015548</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+      <c r="AA13" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B14" s="4">
-        <v>80160964</v>
+        <v>17976371</v>
       </c>
       <c r="C14" s="4">
-        <v>80183873</v>
+        <v>18074711</v>
       </c>
       <c r="D14" s="4">
-        <v>640</v>
+        <v>3913</v>
       </c>
       <c r="E14" s="4">
-        <v>1191.1170669999999</v>
+        <v>2870.176172</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G14" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H14" s="4">
-        <v>80165838</v>
+        <v>17962052</v>
       </c>
       <c r="I14" s="4">
-        <v>80178577</v>
+        <v>18060780</v>
       </c>
       <c r="J14" s="4">
-        <v>42</v>
+        <v>2429</v>
       </c>
       <c r="K14" s="4">
-        <v>1700.847135</v>
+        <v>3450.7886920000001</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M14" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14" s="4">
-        <v>80161669</v>
+        <v>17997545</v>
       </c>
       <c r="O14" s="4">
-        <v>80189103</v>
+        <v>18052601</v>
       </c>
       <c r="P14" s="4">
-        <v>615</v>
+        <v>882</v>
       </c>
       <c r="Q14" s="4">
-        <v>1834.9834739999999</v>
+        <v>1867.4453060000001</v>
       </c>
       <c r="R14" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S14" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" s="4">
-        <v>80175492</v>
+        <v>18061046</v>
       </c>
       <c r="U14" s="4">
-        <v>80180787</v>
+        <v>18065942</v>
       </c>
       <c r="V14" s="4" t="s">
         <v>26</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Z14" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15">
-        <v>77639188</v>
-      </c>
-      <c r="C15">
-        <v>77697871</v>
-      </c>
-      <c r="D15">
-        <v>1042</v>
-      </c>
-      <c r="E15">
-        <v>1456.8155650000001</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="AA14" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
+        <v>40749771</v>
+      </c>
+      <c r="C15" s="4">
+        <v>40779522</v>
+      </c>
+      <c r="D15" s="4">
+        <v>793</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1277.745809</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-      <c r="H15">
-        <v>77650886</v>
-      </c>
-      <c r="I15">
-        <v>77664009</v>
-      </c>
-      <c r="J15">
-        <v>92</v>
-      </c>
-      <c r="K15">
-        <v>1740.6528450000001</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="G15" s="4">
+        <v>6</v>
+      </c>
+      <c r="H15" s="4">
+        <v>40757023</v>
+      </c>
+      <c r="I15" s="4">
+        <v>40776665</v>
+      </c>
+      <c r="J15" s="4">
+        <v>385</v>
+      </c>
+      <c r="K15" s="4">
+        <v>1800.2435310000001</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="M15">
-        <v>3</v>
-      </c>
-      <c r="N15">
-        <v>77639086</v>
-      </c>
-      <c r="O15">
-        <v>77673734</v>
-      </c>
-      <c r="P15">
-        <v>652</v>
-      </c>
-      <c r="Q15">
-        <v>1656.0932660000001</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="M15" s="4">
+        <v>6</v>
+      </c>
+      <c r="N15" s="4">
+        <v>40759889</v>
+      </c>
+      <c r="O15" s="4">
+        <v>40770830</v>
+      </c>
+      <c r="P15" s="4">
+        <v>45</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>1139.2922329999999</v>
+      </c>
+      <c r="R15" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="S15">
-        <v>3</v>
-      </c>
-      <c r="T15">
-        <v>77651713</v>
-      </c>
-      <c r="U15">
-        <v>77656954</v>
-      </c>
-      <c r="V15" t="s">
-        <v>26</v>
-      </c>
-      <c r="W15" t="s">
-        <v>105</v>
-      </c>
-      <c r="X15" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>310</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S15" s="4">
+        <v>6</v>
+      </c>
+      <c r="T15" s="4">
+        <v>40744456</v>
+      </c>
+      <c r="U15" s="4">
+        <v>40752372</v>
+      </c>
+      <c r="V15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="X15" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y15" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z15" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA15" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B16" s="4">
-        <v>63052282</v>
+        <v>56227592</v>
       </c>
       <c r="C16" s="4">
-        <v>63092572</v>
+        <v>56261449</v>
       </c>
       <c r="D16" s="4">
-        <v>825</v>
+        <v>587</v>
       </c>
       <c r="E16" s="4">
-        <v>1521.3566880000001</v>
+        <v>1454.591242</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G16" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H16" s="4">
-        <v>63062915</v>
+        <v>56233983</v>
       </c>
       <c r="I16" s="4">
-        <v>63086509</v>
+        <v>56244499</v>
       </c>
       <c r="J16" s="4">
-        <v>423</v>
+        <v>3</v>
       </c>
       <c r="K16" s="4">
-        <v>1814.0876330000001</v>
+        <v>1693.8803969999999</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M16" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N16" s="4">
-        <v>63059302</v>
+        <v>56220525</v>
       </c>
       <c r="O16" s="4">
-        <v>63084877</v>
+        <v>56255193</v>
       </c>
       <c r="P16" s="4">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="Q16" s="4">
-        <v>1370.5586989999999</v>
+        <v>2029.2391689999999</v>
       </c>
       <c r="R16" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S16" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T16" s="4">
-        <v>63085267</v>
+        <v>56243786</v>
       </c>
       <c r="U16" s="4">
-        <v>63097361</v>
+        <v>56252025</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>89</v>
+        <v>259</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>5</v>
-      </c>
-      <c r="B17">
-        <v>66794715</v>
-      </c>
-      <c r="C17">
-        <v>66833854</v>
-      </c>
-      <c r="D17">
-        <v>862</v>
-      </c>
-      <c r="E17">
-        <v>1323.865579</v>
-      </c>
-      <c r="F17" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA16" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
+        <v>9</v>
+      </c>
+      <c r="B17" s="4">
+        <v>4169437</v>
+      </c>
+      <c r="C17" s="4">
+        <v>4217545</v>
+      </c>
+      <c r="D17" s="4">
+        <v>723</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1810.86626</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-      <c r="H17">
-        <v>66799083</v>
-      </c>
-      <c r="I17">
-        <v>66811798</v>
-      </c>
-      <c r="J17">
-        <v>234</v>
-      </c>
-      <c r="K17">
-        <v>1748.575531</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="G17" s="4">
+        <v>9</v>
+      </c>
+      <c r="H17" s="4">
+        <v>4179846</v>
+      </c>
+      <c r="I17" s="4">
+        <v>4191340</v>
+      </c>
+      <c r="J17" s="4">
+        <v>4</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1755.0552279999999</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="M17">
-        <v>5</v>
-      </c>
-      <c r="N17">
-        <v>66793942</v>
-      </c>
-      <c r="O17">
-        <v>66822158</v>
-      </c>
-      <c r="P17">
-        <v>690</v>
-      </c>
-      <c r="Q17">
-        <v>1935.7218339999999</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="M17" s="4">
+        <v>9</v>
+      </c>
+      <c r="N17" s="4">
+        <v>4191356</v>
+      </c>
+      <c r="O17" s="4">
+        <v>4211587</v>
+      </c>
+      <c r="P17" s="4">
+        <v>477</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>1329.908889</v>
+      </c>
+      <c r="R17" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="S17">
-        <v>5</v>
-      </c>
-      <c r="T17">
-        <v>66811849</v>
-      </c>
-      <c r="U17">
-        <v>66826363</v>
-      </c>
-      <c r="V17" t="s">
+      <c r="S17" s="4">
+        <v>9</v>
+      </c>
+      <c r="T17" s="4">
+        <v>4164654</v>
+      </c>
+      <c r="U17" s="4">
+        <v>4170098</v>
+      </c>
+      <c r="V17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W17" t="s">
-        <v>172</v>
-      </c>
-      <c r="X17" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>292</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W17" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="Z17" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="AA17" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B18" s="4">
-        <v>63994501</v>
+        <v>10905964</v>
       </c>
       <c r="C18" s="4">
-        <v>64034128</v>
+        <v>10931675</v>
       </c>
       <c r="D18" s="4">
-        <v>1317</v>
+        <v>898</v>
       </c>
       <c r="E18" s="4">
-        <v>1293.8785130000001</v>
+        <v>1341.198533</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G18" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H18" s="4">
-        <v>63999374</v>
+        <v>10882047</v>
       </c>
       <c r="I18" s="4">
-        <v>64076061</v>
+        <v>11003407</v>
       </c>
       <c r="J18" s="4">
-        <v>1294</v>
+        <v>2949</v>
       </c>
       <c r="K18" s="4">
-        <v>3430.8111159999999</v>
+        <v>3981.7073989999999</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M18" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N18" s="4">
-        <v>63985680</v>
+        <v>10887578</v>
       </c>
       <c r="O18" s="4">
-        <v>64044018</v>
+        <v>11044608</v>
       </c>
       <c r="P18" s="4">
-        <v>1458</v>
+        <v>5371</v>
       </c>
       <c r="Q18" s="4">
-        <v>2731.3774370000001</v>
+        <v>5841.2801280000003</v>
       </c>
       <c r="R18" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S18" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" s="4">
-        <v>64009875</v>
+        <v>10907169</v>
       </c>
       <c r="U18" s="4">
-        <v>64015548</v>
+        <v>10913953</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>164</v>
+        <v>241</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Z18" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>5</v>
-      </c>
-      <c r="B19">
-        <v>60037141</v>
-      </c>
-      <c r="C19">
-        <v>60054027</v>
-      </c>
-      <c r="D19">
-        <v>156</v>
-      </c>
-      <c r="E19">
-        <v>875.6588577</v>
-      </c>
-      <c r="F19" t="s">
-        <v>322</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-      <c r="H19">
-        <v>60042038</v>
-      </c>
-      <c r="I19">
-        <v>60090345</v>
-      </c>
-      <c r="J19">
-        <v>574</v>
-      </c>
-      <c r="K19">
-        <v>2792.2303339999999</v>
-      </c>
-      <c r="L19" t="s">
-        <v>324</v>
-      </c>
-      <c r="M19">
-        <v>5</v>
-      </c>
-      <c r="N19">
-        <v>60032848</v>
-      </c>
-      <c r="O19">
-        <v>60090345</v>
-      </c>
-      <c r="P19">
-        <v>1213</v>
-      </c>
-      <c r="Q19">
-        <v>2028.8232230000001</v>
-      </c>
-      <c r="R19" t="s">
-        <v>323</v>
-      </c>
-      <c r="S19">
-        <v>5</v>
-      </c>
-      <c r="T19">
-        <v>60033661</v>
-      </c>
-      <c r="U19">
-        <v>60041703</v>
-      </c>
-      <c r="V19" t="s">
-        <v>26</v>
-      </c>
-      <c r="W19" t="s">
-        <v>156</v>
-      </c>
-      <c r="X19" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>5</v>
-      </c>
-      <c r="B20">
-        <v>17976371</v>
-      </c>
-      <c r="C20">
-        <v>18074711</v>
-      </c>
-      <c r="D20">
-        <v>3913</v>
-      </c>
-      <c r="E20">
-        <v>2870.176172</v>
-      </c>
-      <c r="F20" t="s">
-        <v>322</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-      <c r="H20">
-        <v>17962052</v>
-      </c>
-      <c r="I20">
-        <v>18060780</v>
-      </c>
-      <c r="J20">
-        <v>2429</v>
-      </c>
-      <c r="K20">
-        <v>3450.7886920000001</v>
-      </c>
-      <c r="L20" t="s">
-        <v>324</v>
-      </c>
-      <c r="M20">
-        <v>5</v>
-      </c>
-      <c r="N20">
-        <v>17997545</v>
-      </c>
-      <c r="O20">
-        <v>18052601</v>
-      </c>
-      <c r="P20">
-        <v>882</v>
-      </c>
-      <c r="Q20">
-        <v>1867.4453060000001</v>
-      </c>
-      <c r="R20" t="s">
-        <v>323</v>
-      </c>
-      <c r="S20">
-        <v>5</v>
-      </c>
-      <c r="T20">
-        <v>17978616</v>
-      </c>
-      <c r="U20">
-        <v>17984142</v>
-      </c>
-      <c r="V20" t="s">
-        <v>21</v>
-      </c>
-      <c r="W20" t="s">
-        <v>147</v>
-      </c>
-      <c r="X20" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>303</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>5</v>
-      </c>
-      <c r="B21">
-        <v>55893417</v>
-      </c>
-      <c r="C21">
-        <v>55975602</v>
-      </c>
-      <c r="D21">
-        <v>1449</v>
-      </c>
-      <c r="E21">
-        <v>2403.3722240000002</v>
-      </c>
-      <c r="F21" t="s">
-        <v>322</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-      <c r="H21">
-        <v>55883506</v>
-      </c>
-      <c r="I21">
-        <v>55975636</v>
-      </c>
-      <c r="J21">
-        <v>988</v>
-      </c>
-      <c r="K21">
-        <v>4008.6207720000002</v>
-      </c>
-      <c r="L21" t="s">
-        <v>324</v>
-      </c>
-      <c r="M21">
-        <v>5</v>
-      </c>
-      <c r="N21">
-        <v>55893417</v>
-      </c>
-      <c r="O21">
-        <v>55975636</v>
-      </c>
-      <c r="P21">
-        <v>1307</v>
-      </c>
-      <c r="Q21">
-        <v>2481.1233579999998</v>
-      </c>
-      <c r="R21" t="s">
-        <v>323</v>
-      </c>
-      <c r="S21">
-        <v>5</v>
-      </c>
-      <c r="T21">
-        <v>55948634</v>
-      </c>
-      <c r="U21">
-        <v>55969293</v>
-      </c>
-      <c r="V21" t="s">
-        <v>21</v>
-      </c>
-      <c r="W21" t="s">
-        <v>155</v>
-      </c>
-      <c r="X21" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>311</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
-        <v>5</v>
-      </c>
-      <c r="B22" s="4">
-        <v>17976371</v>
-      </c>
-      <c r="C22" s="4">
-        <v>18074711</v>
-      </c>
-      <c r="D22" s="4">
-        <v>3913</v>
-      </c>
-      <c r="E22" s="4">
-        <v>2870.176172</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="G22" s="4">
-        <v>5</v>
-      </c>
-      <c r="H22" s="4">
-        <v>17962052</v>
-      </c>
-      <c r="I22" s="4">
-        <v>18060780</v>
-      </c>
-      <c r="J22" s="4">
-        <v>2429</v>
-      </c>
-      <c r="K22" s="4">
-        <v>3450.7886920000001</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="M22" s="4">
-        <v>5</v>
-      </c>
-      <c r="N22" s="4">
-        <v>17997545</v>
-      </c>
-      <c r="O22" s="4">
-        <v>18052601</v>
-      </c>
-      <c r="P22" s="4">
-        <v>882</v>
-      </c>
-      <c r="Q22" s="4">
-        <v>1867.4453060000001</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="S22" s="4">
-        <v>5</v>
-      </c>
-      <c r="T22" s="4">
-        <v>18061046</v>
-      </c>
-      <c r="U22" s="4">
-        <v>18065942</v>
-      </c>
-      <c r="V22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="W22" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="X22" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y22" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z22" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>5</v>
-      </c>
-      <c r="B23">
-        <v>60056455</v>
-      </c>
-      <c r="C23">
-        <v>60090345</v>
-      </c>
-      <c r="D23">
-        <v>395</v>
-      </c>
-      <c r="E23">
-        <v>1469.1876150000001</v>
-      </c>
-      <c r="F23" t="s">
-        <v>322</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-      <c r="H23">
-        <v>60042038</v>
-      </c>
-      <c r="I23">
-        <v>60090345</v>
-      </c>
-      <c r="J23">
-        <v>574</v>
-      </c>
-      <c r="K23">
-        <v>2792.2303339999999</v>
-      </c>
-      <c r="L23" t="s">
-        <v>324</v>
-      </c>
-      <c r="M23">
-        <v>5</v>
-      </c>
-      <c r="N23">
-        <v>60032848</v>
-      </c>
-      <c r="O23">
-        <v>60090345</v>
-      </c>
-      <c r="P23">
-        <v>1213</v>
-      </c>
-      <c r="Q23">
-        <v>2028.8232230000001</v>
-      </c>
-      <c r="R23" t="s">
-        <v>323</v>
-      </c>
-      <c r="S23">
-        <v>5</v>
-      </c>
-      <c r="T23">
-        <v>60070226</v>
-      </c>
-      <c r="U23">
-        <v>60078146</v>
-      </c>
-      <c r="V23" t="s">
-        <v>26</v>
-      </c>
-      <c r="W23" t="s">
-        <v>158</v>
-      </c>
-      <c r="X23" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>5</v>
-      </c>
-      <c r="B24">
-        <v>66794715</v>
-      </c>
-      <c r="C24">
-        <v>66833854</v>
-      </c>
-      <c r="D24">
-        <v>862</v>
-      </c>
-      <c r="E24">
-        <v>1323.865579</v>
-      </c>
-      <c r="F24" t="s">
-        <v>322</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-      <c r="H24">
-        <v>66799083</v>
-      </c>
-      <c r="I24">
-        <v>66811798</v>
-      </c>
-      <c r="J24">
-        <v>234</v>
-      </c>
-      <c r="K24">
-        <v>1748.575531</v>
-      </c>
-      <c r="L24" t="s">
-        <v>324</v>
-      </c>
-      <c r="M24">
-        <v>5</v>
-      </c>
-      <c r="N24">
-        <v>66793942</v>
-      </c>
-      <c r="O24">
-        <v>66822158</v>
-      </c>
-      <c r="P24">
-        <v>690</v>
-      </c>
-      <c r="Q24">
-        <v>1935.7218339999999</v>
-      </c>
-      <c r="R24" t="s">
-        <v>323</v>
-      </c>
-      <c r="S24">
-        <v>5</v>
-      </c>
-      <c r="T24">
-        <v>66826106</v>
-      </c>
-      <c r="U24">
-        <v>66833703</v>
-      </c>
-      <c r="V24" t="s">
-        <v>26</v>
-      </c>
-      <c r="W24" t="s">
-        <v>174</v>
-      </c>
-      <c r="X24" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>308</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
-        <v>6</v>
-      </c>
-      <c r="B25" s="4">
-        <v>40749771</v>
-      </c>
-      <c r="C25" s="4">
-        <v>40779522</v>
-      </c>
-      <c r="D25" s="4">
-        <v>793</v>
-      </c>
-      <c r="E25" s="4">
-        <v>1277.745809</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="G25" s="4">
-        <v>6</v>
-      </c>
-      <c r="H25" s="4">
-        <v>40757023</v>
-      </c>
-      <c r="I25" s="4">
-        <v>40776665</v>
-      </c>
-      <c r="J25" s="4">
-        <v>385</v>
-      </c>
-      <c r="K25" s="4">
-        <v>1800.2435310000001</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="M25" s="4">
-        <v>6</v>
-      </c>
-      <c r="N25" s="4">
-        <v>40759889</v>
-      </c>
-      <c r="O25" s="4">
-        <v>40770830</v>
-      </c>
-      <c r="P25" s="4">
-        <v>45</v>
-      </c>
-      <c r="Q25" s="4">
-        <v>1139.2922329999999</v>
-      </c>
-      <c r="R25" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="S25" s="4">
-        <v>6</v>
-      </c>
-      <c r="T25" s="4">
-        <v>40744456</v>
-      </c>
-      <c r="U25" s="4">
-        <v>40752372</v>
-      </c>
-      <c r="V25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="W25" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="Y25" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z25" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>6</v>
-      </c>
-      <c r="B26">
-        <v>62571718</v>
-      </c>
-      <c r="C26">
-        <v>62633936</v>
-      </c>
-      <c r="D26">
-        <v>1964</v>
-      </c>
-      <c r="E26">
-        <v>1616.2311400000001</v>
-      </c>
-      <c r="F26" t="s">
-        <v>322</v>
-      </c>
-      <c r="G26">
-        <v>6</v>
-      </c>
-      <c r="H26">
-        <v>62552160</v>
-      </c>
-      <c r="I26">
-        <v>62656998</v>
-      </c>
-      <c r="J26">
-        <v>1763</v>
-      </c>
-      <c r="K26">
-        <v>3006.5383579999998</v>
-      </c>
-      <c r="L26" t="s">
-        <v>324</v>
-      </c>
-      <c r="M26">
-        <v>6</v>
-      </c>
-      <c r="N26">
-        <v>62558231</v>
-      </c>
-      <c r="O26">
-        <v>62656998</v>
-      </c>
-      <c r="P26">
-        <v>2098</v>
-      </c>
-      <c r="Q26">
-        <v>3012.54315</v>
-      </c>
-      <c r="R26" t="s">
-        <v>323</v>
-      </c>
-      <c r="S26">
-        <v>6</v>
-      </c>
-      <c r="T26">
-        <v>62594307</v>
-      </c>
-      <c r="U26">
-        <v>62602526</v>
-      </c>
-      <c r="V26" t="s">
-        <v>26</v>
-      </c>
-      <c r="W26" t="s">
-        <v>188</v>
-      </c>
-      <c r="X26" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>307</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>8</v>
-      </c>
-      <c r="B27">
-        <v>53859711</v>
-      </c>
-      <c r="C27">
-        <v>53918865</v>
-      </c>
-      <c r="D27">
-        <v>1224</v>
-      </c>
-      <c r="E27">
-        <v>1112.4084089999999</v>
-      </c>
-      <c r="F27" t="s">
-        <v>322</v>
-      </c>
-      <c r="G27">
-        <v>8</v>
-      </c>
-      <c r="H27">
-        <v>53865800</v>
-      </c>
-      <c r="I27">
-        <v>53917279</v>
-      </c>
-      <c r="J27">
-        <v>720</v>
-      </c>
-      <c r="K27">
-        <v>3150.5423249999999</v>
-      </c>
-      <c r="L27" t="s">
-        <v>324</v>
-      </c>
-      <c r="M27">
-        <v>8</v>
-      </c>
-      <c r="N27">
-        <v>53848986</v>
-      </c>
-      <c r="O27">
-        <v>53905037</v>
-      </c>
-      <c r="P27">
-        <v>1013</v>
-      </c>
-      <c r="Q27">
-        <v>2165.9072460000002</v>
-      </c>
-      <c r="R27" t="s">
-        <v>323</v>
-      </c>
-      <c r="S27">
-        <v>8</v>
-      </c>
-      <c r="T27">
-        <v>53917949</v>
-      </c>
-      <c r="U27">
-        <v>53923696</v>
-      </c>
-      <c r="V27" t="s">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s">
-        <v>232</v>
-      </c>
-      <c r="X27" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>317</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>8</v>
-      </c>
-      <c r="B28">
-        <v>5246665</v>
-      </c>
-      <c r="C28">
-        <v>5297043</v>
-      </c>
-      <c r="D28">
-        <v>1859</v>
-      </c>
-      <c r="E28">
-        <v>2050.4465030000001</v>
-      </c>
-      <c r="F28" t="s">
-        <v>322</v>
-      </c>
-      <c r="G28">
-        <v>8</v>
-      </c>
-      <c r="H28">
-        <v>5248198</v>
-      </c>
-      <c r="I28">
-        <v>5273656</v>
-      </c>
-      <c r="J28">
-        <v>363</v>
-      </c>
-      <c r="K28">
-        <v>2147.8199300000001</v>
-      </c>
-      <c r="L28" t="s">
-        <v>324</v>
-      </c>
-      <c r="M28">
-        <v>8</v>
-      </c>
-      <c r="N28">
-        <v>5248064</v>
-      </c>
-      <c r="O28">
-        <v>5272904</v>
-      </c>
-      <c r="P28">
-        <v>401</v>
-      </c>
-      <c r="Q28">
-        <v>1497.6168479999999</v>
-      </c>
-      <c r="R28" t="s">
-        <v>323</v>
-      </c>
-      <c r="S28">
-        <v>8</v>
-      </c>
-      <c r="T28">
-        <v>5274483</v>
-      </c>
-      <c r="U28">
-        <v>5282132</v>
-      </c>
-      <c r="V28" t="s">
-        <v>21</v>
-      </c>
-      <c r="W28" t="s">
-        <v>228</v>
-      </c>
-      <c r="X28" t="s">
-        <v>229</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>310</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
-        <v>9</v>
-      </c>
-      <c r="B29" s="4">
-        <v>56227592</v>
-      </c>
-      <c r="C29" s="4">
-        <v>56261449</v>
-      </c>
-      <c r="D29" s="4">
-        <v>587</v>
-      </c>
-      <c r="E29" s="4">
-        <v>1454.591242</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="G29" s="4">
-        <v>9</v>
-      </c>
-      <c r="H29" s="4">
-        <v>56233983</v>
-      </c>
-      <c r="I29" s="4">
-        <v>56244499</v>
-      </c>
-      <c r="J29" s="4">
-        <v>3</v>
-      </c>
-      <c r="K29" s="4">
-        <v>1693.8803969999999</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="M29" s="4">
-        <v>9</v>
-      </c>
-      <c r="N29" s="4">
-        <v>56220525</v>
-      </c>
-      <c r="O29" s="4">
-        <v>56255193</v>
-      </c>
-      <c r="P29" s="4">
-        <v>554</v>
-      </c>
-      <c r="Q29" s="4">
-        <v>2029.2391689999999</v>
-      </c>
-      <c r="R29" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="S29" s="4">
-        <v>9</v>
-      </c>
-      <c r="T29" s="4">
-        <v>56243786</v>
-      </c>
-      <c r="U29" s="4">
-        <v>56252025</v>
-      </c>
-      <c r="V29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="W29" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="X29" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="Y29" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z29" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
-        <v>9</v>
-      </c>
-      <c r="B30" s="4">
-        <v>4169437</v>
-      </c>
-      <c r="C30" s="4">
-        <v>4217545</v>
-      </c>
-      <c r="D30" s="4">
-        <v>723</v>
-      </c>
-      <c r="E30" s="4">
-        <v>1810.86626</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="G30" s="4">
-        <v>9</v>
-      </c>
-      <c r="H30" s="4">
-        <v>4179846</v>
-      </c>
-      <c r="I30" s="4">
-        <v>4191340</v>
-      </c>
-      <c r="J30" s="4">
-        <v>4</v>
-      </c>
-      <c r="K30" s="4">
-        <v>1755.0552279999999</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="M30" s="4">
-        <v>9</v>
-      </c>
-      <c r="N30" s="4">
-        <v>4191356</v>
-      </c>
-      <c r="O30" s="4">
-        <v>4211587</v>
-      </c>
-      <c r="P30" s="4">
-        <v>477</v>
-      </c>
-      <c r="Q30" s="4">
-        <v>1329.908889</v>
-      </c>
-      <c r="R30" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="S30" s="4">
-        <v>9</v>
-      </c>
-      <c r="T30" s="4">
-        <v>4164654</v>
-      </c>
-      <c r="U30" s="4">
-        <v>4170098</v>
-      </c>
-      <c r="V30" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="W30" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="X30" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y30" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="Z30" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
-        <v>9</v>
-      </c>
-      <c r="B31" s="4">
-        <v>10905964</v>
-      </c>
-      <c r="C31" s="4">
-        <v>10931675</v>
-      </c>
-      <c r="D31" s="4">
-        <v>898</v>
-      </c>
-      <c r="E31" s="4">
-        <v>1341.198533</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="G31" s="4">
-        <v>9</v>
-      </c>
-      <c r="H31" s="4">
-        <v>10882047</v>
-      </c>
-      <c r="I31" s="4">
-        <v>11003407</v>
-      </c>
-      <c r="J31" s="4">
-        <v>2949</v>
-      </c>
-      <c r="K31" s="4">
-        <v>3981.7073989999999</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="M31" s="4">
-        <v>9</v>
-      </c>
-      <c r="N31" s="4">
-        <v>10887578</v>
-      </c>
-      <c r="O31" s="4">
-        <v>11044608</v>
-      </c>
-      <c r="P31" s="4">
-        <v>5371</v>
-      </c>
-      <c r="Q31" s="4">
-        <v>5841.2801280000003</v>
-      </c>
-      <c r="R31" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="S31" s="4">
-        <v>9</v>
-      </c>
-      <c r="T31" s="4">
-        <v>10907169</v>
-      </c>
-      <c r="U31" s="4">
-        <v>10913953</v>
-      </c>
-      <c r="V31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="W31" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="X31" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y31" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="Z31" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>9</v>
-      </c>
-      <c r="B32">
-        <v>56227592</v>
-      </c>
-      <c r="C32">
-        <v>56261449</v>
-      </c>
-      <c r="D32">
-        <v>587</v>
-      </c>
-      <c r="E32">
-        <v>1454.591242</v>
-      </c>
-      <c r="F32" t="s">
-        <v>322</v>
-      </c>
-      <c r="G32">
-        <v>9</v>
-      </c>
-      <c r="H32">
-        <v>56233983</v>
-      </c>
-      <c r="I32">
-        <v>56244499</v>
-      </c>
-      <c r="J32">
-        <v>3</v>
-      </c>
-      <c r="K32">
-        <v>1693.8803969999999</v>
-      </c>
-      <c r="L32" t="s">
-        <v>324</v>
-      </c>
-      <c r="M32">
-        <v>9</v>
-      </c>
-      <c r="N32">
-        <v>56220525</v>
-      </c>
-      <c r="O32">
-        <v>56255193</v>
-      </c>
-      <c r="P32">
-        <v>554</v>
-      </c>
-      <c r="Q32">
-        <v>2029.2391689999999</v>
-      </c>
-      <c r="R32" t="s">
-        <v>323</v>
-      </c>
-      <c r="S32">
-        <v>9</v>
-      </c>
-      <c r="T32">
-        <v>56228137</v>
-      </c>
-      <c r="U32">
-        <v>56233826</v>
-      </c>
-      <c r="V32" t="s">
-        <v>26</v>
-      </c>
-      <c r="W32" t="s">
-        <v>261</v>
-      </c>
-      <c r="X32" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>9</v>
-      </c>
-      <c r="B33">
-        <v>54793129</v>
-      </c>
-      <c r="C33">
-        <v>54843426</v>
-      </c>
-      <c r="D33">
-        <v>2024</v>
-      </c>
-      <c r="E33">
-        <v>2566.6429370000001</v>
-      </c>
-      <c r="F33" t="s">
-        <v>322</v>
-      </c>
-      <c r="G33">
-        <v>9</v>
-      </c>
-      <c r="H33">
-        <v>54772169</v>
-      </c>
-      <c r="I33">
-        <v>54837075</v>
-      </c>
-      <c r="J33">
-        <v>1809</v>
-      </c>
-      <c r="K33">
-        <v>3343.9049230000001</v>
-      </c>
-      <c r="L33" t="s">
-        <v>324</v>
-      </c>
-      <c r="M33">
-        <v>9</v>
-      </c>
-      <c r="N33">
-        <v>54772169</v>
-      </c>
-      <c r="O33">
-        <v>54800560</v>
-      </c>
-      <c r="P33">
-        <v>740</v>
-      </c>
-      <c r="Q33">
-        <v>1824.7336049999999</v>
-      </c>
-      <c r="R33" t="s">
-        <v>323</v>
-      </c>
-      <c r="S33">
-        <v>9</v>
-      </c>
-      <c r="T33">
-        <v>54831300</v>
-      </c>
-      <c r="U33">
-        <v>54836736</v>
-      </c>
-      <c r="V33" t="s">
-        <v>26</v>
-      </c>
-      <c r="W33" t="s">
-        <v>250</v>
-      </c>
-      <c r="X33" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>307</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>10</v>
-      </c>
-      <c r="B34">
-        <v>8229126</v>
-      </c>
-      <c r="C34">
-        <v>8287175</v>
-      </c>
-      <c r="D34">
-        <v>1408</v>
-      </c>
-      <c r="E34">
-        <v>1396.3279460000001</v>
-      </c>
-      <c r="F34" t="s">
-        <v>322</v>
-      </c>
-      <c r="G34">
-        <v>10</v>
-      </c>
-      <c r="H34">
-        <v>8204008</v>
-      </c>
-      <c r="I34">
-        <v>8287597</v>
-      </c>
-      <c r="J34">
-        <v>1149</v>
-      </c>
-      <c r="K34">
-        <v>2470.792488</v>
-      </c>
-      <c r="L34" t="s">
-        <v>324</v>
-      </c>
-      <c r="M34">
-        <v>10</v>
-      </c>
-      <c r="N34">
-        <v>8218749</v>
-      </c>
-      <c r="O34">
-        <v>8288131</v>
-      </c>
-      <c r="P34">
-        <v>1449</v>
-      </c>
-      <c r="Q34">
-        <v>2466.6055900000001</v>
-      </c>
-      <c r="R34" t="s">
-        <v>323</v>
-      </c>
-      <c r="S34">
-        <v>10</v>
-      </c>
-      <c r="T34">
-        <v>8225859</v>
-      </c>
-      <c r="U34">
-        <v>8230786</v>
-      </c>
-      <c r="V34" t="s">
-        <v>21</v>
-      </c>
-      <c r="W34" t="s">
-        <v>268</v>
-      </c>
-      <c r="X34" t="s">
-        <v>269</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>289</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>288</v>
+      <c r="AA18" s="4" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z35">
-    <sortCondition ref="S2:S35"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z19">
+    <sortCondition ref="S2:S19"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2.0_balancing_selection/01_b2_candidates/W_L_I_5kb_description.xlsx
+++ b/data/2.0_balancing_selection/01_b2_candidates/W_L_I_5kb_description.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/2.0_balancing_selection/01_b2_candidates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743504B8-7420-E344-AA0C-BCCBAE33A94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98386453-FC3B-9644-A6EA-4D07BF62A1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35280" yWindow="4280" windowWidth="27040" windowHeight="15760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27040" yWindow="-5200" windowWidth="51200" windowHeight="28180" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18137,7 +18137,7 @@
       <c r="D18" s="4">
         <v>5371</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="4">
         <v>3689.872711</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -18155,7 +18155,7 @@
       <c r="J18" s="4">
         <v>2949</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="4">
         <v>3689.872711</v>
       </c>
       <c r="L18" s="4" t="s">

--- a/data/2.0_balancing_selection/01_b2_candidates/W_L_I_5kb_description.xlsx
+++ b/data/2.0_balancing_selection/01_b2_candidates/W_L_I_5kb_description.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/2.0_balancing_selection/01_b2_candidates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98386453-FC3B-9644-A6EA-4D07BF62A1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AEBDC7-4FA0-BB46-9264-8553A39B3A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27040" yWindow="-5200" windowWidth="51200" windowHeight="28180" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="336">
   <si>
     <t>V1</t>
   </si>
@@ -1037,6 +1037,18 @@
   </si>
   <si>
     <t>#1f78b</t>
+  </si>
+  <si>
+    <t>landraace</t>
+  </si>
+  <si>
+    <t>improved</t>
+  </si>
+  <si>
+    <t>gene</t>
+  </si>
+  <si>
+    <t>gene_group</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1103,6 +1115,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16714,255 +16730,126 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBEA331F-FAF3-FA4D-99BA-09633F6307B7}">
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A2:AA20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="24" max="24" width="49.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Z2" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1" t="s">
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1" t="s">
+      <c r="R3" s="1"/>
+      <c r="S3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4">
-        <v>76251349</v>
-      </c>
-      <c r="C2" s="4">
-        <v>76288737</v>
-      </c>
-      <c r="D2" s="4">
-        <v>542</v>
-      </c>
-      <c r="E2" s="4">
-        <v>1272.7086059999999</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="G2" s="4">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4">
-        <v>76236063</v>
-      </c>
-      <c r="I2" s="4">
-        <v>76300277</v>
-      </c>
-      <c r="J2" s="4">
-        <v>874</v>
-      </c>
-      <c r="K2" s="4">
-        <v>2341.7856270000002</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="M2" s="4">
-        <v>1</v>
-      </c>
-      <c r="N2" s="4">
-        <v>76245602</v>
-      </c>
-      <c r="O2" s="4">
-        <v>76281143</v>
-      </c>
-      <c r="P2" s="4">
-        <v>587</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>1680.6402250000001</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="S2" s="4">
-        <v>1</v>
-      </c>
-      <c r="T2" s="4">
-        <v>76249893</v>
-      </c>
-      <c r="U2" s="4">
-        <v>76259302</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4">
-        <v>76251349</v>
-      </c>
-      <c r="C3" s="4">
-        <v>76288737</v>
-      </c>
-      <c r="D3" s="4">
-        <v>542</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1272.7086059999999</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4">
-        <v>76236063</v>
-      </c>
-      <c r="I3" s="4">
-        <v>76300277</v>
-      </c>
-      <c r="J3" s="4">
-        <v>874</v>
-      </c>
-      <c r="K3" s="4">
-        <v>2341.7856270000002</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="M3" s="4">
-        <v>1</v>
-      </c>
-      <c r="N3" s="4">
-        <v>76245602</v>
-      </c>
-      <c r="O3" s="4">
-        <v>76281143</v>
-      </c>
-      <c r="P3" s="4">
-        <v>587</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>1680.6402250000001</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="S3" s="4">
-        <v>1</v>
-      </c>
-      <c r="T3" s="4">
-        <v>76267464</v>
-      </c>
-      <c r="U3" s="4">
-        <v>76274683</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -17021,16 +16908,16 @@
         <v>1</v>
       </c>
       <c r="T4" s="4">
-        <v>76273014</v>
+        <v>76249893</v>
       </c>
       <c r="U4" s="4">
-        <v>76281245</v>
+        <v>76259302</v>
       </c>
       <c r="V4" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="X4" s="4" t="s">
         <v>312</v>
@@ -17041,174 +16928,174 @@
       <c r="Z4" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="AA4" s="4" t="s">
+      <c r="AA4" s="5" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="4">
-        <v>9525692</v>
+        <v>76251349</v>
       </c>
       <c r="C5" s="4">
-        <v>9552494</v>
+        <v>76288737</v>
       </c>
       <c r="D5" s="4">
-        <v>237</v>
+        <v>542</v>
       </c>
       <c r="E5" s="4">
-        <v>994.83566099999996</v>
+        <v>1272.7086059999999</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="4">
-        <v>9543928</v>
+        <v>76236063</v>
       </c>
       <c r="I5" s="4">
-        <v>9565990</v>
+        <v>76300277</v>
       </c>
       <c r="J5" s="4">
-        <v>106</v>
+        <v>874</v>
       </c>
       <c r="K5" s="4">
-        <v>1777.271297</v>
+        <v>2341.7856270000002</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>9530109</v>
+        <v>76245602</v>
       </c>
       <c r="O5" s="4">
-        <v>9563088</v>
+        <v>76281143</v>
       </c>
       <c r="P5" s="4">
-        <v>643</v>
+        <v>587</v>
       </c>
       <c r="Q5" s="4">
-        <v>1546.408958</v>
+        <v>1680.6402250000001</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" s="4">
-        <v>9533824</v>
+        <v>76267464</v>
       </c>
       <c r="U5" s="4">
-        <v>9539966</v>
+        <v>76274683</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>40</v>
+        <v>312</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="4">
-        <v>16833284</v>
+        <v>76251349</v>
       </c>
       <c r="C6" s="4">
-        <v>16906729</v>
+        <v>76288737</v>
       </c>
       <c r="D6" s="4">
-        <v>1489</v>
+        <v>542</v>
       </c>
       <c r="E6" s="4">
-        <v>1615.7541639999999</v>
+        <v>1272.7086059999999</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="4">
-        <v>16876435</v>
+        <v>76236063</v>
       </c>
       <c r="I6" s="4">
-        <v>16889098</v>
+        <v>76300277</v>
       </c>
       <c r="J6" s="4">
-        <v>12</v>
+        <v>874</v>
       </c>
       <c r="K6" s="4">
-        <v>1832.3460869999999</v>
+        <v>2341.7856270000002</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>16841388</v>
+        <v>76245602</v>
       </c>
       <c r="O6" s="4">
-        <v>16874528</v>
+        <v>76281143</v>
       </c>
       <c r="P6" s="4">
-        <v>844</v>
+        <v>587</v>
       </c>
       <c r="Q6" s="4">
-        <v>1882.994557</v>
+        <v>1680.6402250000001</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" s="4">
-        <v>16841393</v>
+        <v>76273014</v>
       </c>
       <c r="U6" s="4">
-        <v>16846866</v>
+        <v>76281245</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>45</v>
+        <v>312</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -17216,16 +17103,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="4">
-        <v>3891951</v>
+        <v>9525692</v>
       </c>
       <c r="C7" s="4">
-        <v>3904895</v>
+        <v>9552494</v>
       </c>
       <c r="D7" s="4">
-        <v>178</v>
+        <v>237</v>
       </c>
       <c r="E7" s="4">
-        <v>946.21085140000002</v>
+        <v>994.83566099999996</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>322</v>
@@ -17234,16 +17121,16 @@
         <v>2</v>
       </c>
       <c r="H7" s="4">
-        <v>3891951</v>
+        <v>9543928</v>
       </c>
       <c r="I7" s="4">
-        <v>3904496</v>
+        <v>9565990</v>
       </c>
       <c r="J7" s="4">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="K7" s="4">
-        <v>1766.6600980000001</v>
+        <v>1777.271297</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>324</v>
@@ -17252,16 +17139,16 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>3884986</v>
+        <v>9530109</v>
       </c>
       <c r="O7" s="4">
-        <v>3912663</v>
+        <v>9563088</v>
       </c>
       <c r="P7" s="4">
-        <v>559</v>
+        <v>643</v>
       </c>
       <c r="Q7" s="4">
-        <v>1783.198664</v>
+        <v>1546.408958</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>323</v>
@@ -17270,188 +17157,188 @@
         <v>2</v>
       </c>
       <c r="T7" s="4">
-        <v>3884552</v>
+        <v>9533824</v>
       </c>
       <c r="U7" s="4">
-        <v>3902872</v>
+        <v>9539966</v>
       </c>
       <c r="V7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="4">
-        <v>4721370</v>
+        <v>16833284</v>
       </c>
       <c r="C8" s="4">
-        <v>4762544</v>
+        <v>16906729</v>
       </c>
       <c r="D8" s="4">
-        <v>971</v>
+        <v>1489</v>
       </c>
       <c r="E8" s="4">
-        <v>1913.770626</v>
+        <v>1615.7541639999999</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G8" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="4">
-        <v>4736814</v>
+        <v>16876435</v>
       </c>
       <c r="I8" s="4">
-        <v>4754328</v>
+        <v>16889098</v>
       </c>
       <c r="J8" s="4">
-        <v>283</v>
+        <v>12</v>
       </c>
       <c r="K8" s="4">
-        <v>1825.9663539999999</v>
+        <v>1832.3460869999999</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M8" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" s="4">
-        <v>4719612</v>
+        <v>16841388</v>
       </c>
       <c r="O8" s="4">
-        <v>4767808</v>
+        <v>16874528</v>
       </c>
       <c r="P8" s="4">
-        <v>1058</v>
+        <v>844</v>
       </c>
       <c r="Q8" s="4">
-        <v>2654.4997600000002</v>
+        <v>1882.994557</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S8" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" s="4">
-        <v>4730884</v>
+        <v>16841393</v>
       </c>
       <c r="U8" s="4">
-        <v>4739818</v>
+        <v>16846866</v>
       </c>
       <c r="V8" s="4" t="s">
         <v>26</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="4">
-        <v>66577675</v>
+        <v>3891951</v>
       </c>
       <c r="C9" s="4">
-        <v>66660340</v>
+        <v>3904895</v>
       </c>
       <c r="D9" s="4">
-        <v>2148</v>
+        <v>178</v>
       </c>
       <c r="E9" s="4">
-        <v>2737.916577</v>
+        <v>946.21085140000002</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4">
-        <v>66601679</v>
+        <v>3891951</v>
       </c>
       <c r="I9" s="4">
-        <v>66649218</v>
+        <v>3904496</v>
       </c>
       <c r="J9" s="4">
-        <v>1118</v>
+        <v>132</v>
       </c>
       <c r="K9" s="4">
-        <v>2781.4364580000001</v>
+        <v>1766.6600980000001</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" s="4">
-        <v>66582969</v>
+        <v>3884986</v>
       </c>
       <c r="O9" s="4">
-        <v>66662954</v>
+        <v>3912663</v>
       </c>
       <c r="P9" s="4">
-        <v>2272</v>
+        <v>559</v>
       </c>
       <c r="Q9" s="4">
-        <v>4193.4089190000004</v>
+        <v>1783.198664</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" s="4">
-        <v>66576387</v>
+        <v>3884552</v>
       </c>
       <c r="U9" s="4">
-        <v>66582986</v>
+        <v>3902872</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="Z9" s="4" t="s">
         <v>298</v>
@@ -17465,16 +17352,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="4">
-        <v>66577675</v>
+        <v>4721370</v>
       </c>
       <c r="C10" s="4">
-        <v>66660340</v>
+        <v>4762544</v>
       </c>
       <c r="D10" s="4">
-        <v>2148</v>
+        <v>971</v>
       </c>
       <c r="E10" s="4">
-        <v>2737.916577</v>
+        <v>1913.770626</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>322</v>
@@ -17483,16 +17370,16 @@
         <v>3</v>
       </c>
       <c r="H10" s="4">
-        <v>66601679</v>
+        <v>4736814</v>
       </c>
       <c r="I10" s="4">
-        <v>66649218</v>
+        <v>4754328</v>
       </c>
       <c r="J10" s="4">
-        <v>1118</v>
+        <v>283</v>
       </c>
       <c r="K10" s="4">
-        <v>2781.4364580000001</v>
+        <v>1825.9663539999999</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>324</v>
@@ -17501,16 +17388,16 @@
         <v>3</v>
       </c>
       <c r="N10" s="4">
-        <v>66582969</v>
+        <v>4719612</v>
       </c>
       <c r="O10" s="4">
-        <v>66662954</v>
+        <v>4767808</v>
       </c>
       <c r="P10" s="4">
-        <v>2272</v>
+        <v>1058</v>
       </c>
       <c r="Q10" s="4">
-        <v>4193.4089190000004</v>
+        <v>2654.4997600000002</v>
       </c>
       <c r="R10" s="4" t="s">
         <v>323</v>
@@ -17519,16 +17406,16 @@
         <v>3</v>
       </c>
       <c r="T10" s="4">
-        <v>66594310</v>
+        <v>4730884</v>
       </c>
       <c r="U10" s="4">
-        <v>66602908</v>
+        <v>4739818</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="X10" s="4" t="s">
         <v>72</v>
@@ -17548,16 +17435,16 @@
         <v>3</v>
       </c>
       <c r="B11" s="4">
-        <v>80160964</v>
+        <v>66577675</v>
       </c>
       <c r="C11" s="4">
-        <v>80183873</v>
+        <v>66660340</v>
       </c>
       <c r="D11" s="4">
-        <v>640</v>
+        <v>2148</v>
       </c>
       <c r="E11" s="4">
-        <v>1191.1170669999999</v>
+        <v>2737.916577</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>322</v>
@@ -17566,16 +17453,16 @@
         <v>3</v>
       </c>
       <c r="H11" s="4">
-        <v>80165838</v>
+        <v>66601679</v>
       </c>
       <c r="I11" s="4">
-        <v>80178577</v>
+        <v>66649218</v>
       </c>
       <c r="J11" s="4">
-        <v>42</v>
+        <v>1118</v>
       </c>
       <c r="K11" s="4">
-        <v>1700.847135</v>
+        <v>2781.4364580000001</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>324</v>
@@ -17584,16 +17471,16 @@
         <v>3</v>
       </c>
       <c r="N11" s="4">
-        <v>80161669</v>
+        <v>66582969</v>
       </c>
       <c r="O11" s="4">
-        <v>80189103</v>
+        <v>66662954</v>
       </c>
       <c r="P11" s="4">
-        <v>615</v>
+        <v>2272</v>
       </c>
       <c r="Q11" s="4">
-        <v>1834.9834739999999</v>
+        <v>4193.4089190000004</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>323</v>
@@ -17602,28 +17489,28 @@
         <v>3</v>
       </c>
       <c r="T11" s="4">
-        <v>80175492</v>
+        <v>66576387</v>
       </c>
       <c r="U11" s="4">
-        <v>80180787</v>
+        <v>66582986</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AA11" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -17631,16 +17518,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="4">
-        <v>63052282</v>
+        <v>66577675</v>
       </c>
       <c r="C12" s="4">
-        <v>63092572</v>
+        <v>66660340</v>
       </c>
       <c r="D12" s="4">
-        <v>825</v>
+        <v>2148</v>
       </c>
       <c r="E12" s="4">
-        <v>1521.3566880000001</v>
+        <v>2737.916577</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>322</v>
@@ -17649,16 +17536,16 @@
         <v>3</v>
       </c>
       <c r="H12" s="4">
-        <v>63062915</v>
+        <v>66601679</v>
       </c>
       <c r="I12" s="4">
-        <v>63086509</v>
+        <v>66649218</v>
       </c>
       <c r="J12" s="4">
-        <v>423</v>
+        <v>1118</v>
       </c>
       <c r="K12" s="4">
-        <v>1814.0876330000001</v>
+        <v>2781.4364580000001</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>324</v>
@@ -17667,16 +17554,16 @@
         <v>3</v>
       </c>
       <c r="N12" s="4">
-        <v>63059302</v>
+        <v>66582969</v>
       </c>
       <c r="O12" s="4">
-        <v>63084877</v>
+        <v>66662954</v>
       </c>
       <c r="P12" s="4">
-        <v>541</v>
+        <v>2272</v>
       </c>
       <c r="Q12" s="4">
-        <v>1370.5586989999999</v>
+        <v>4193.4089190000004</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>323</v>
@@ -17685,22 +17572,22 @@
         <v>3</v>
       </c>
       <c r="T12" s="4">
-        <v>63085267</v>
+        <v>66594310</v>
       </c>
       <c r="U12" s="4">
-        <v>63097361</v>
+        <v>66602908</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="Z12" s="4" t="s">
         <v>298</v>
@@ -17711,79 +17598,79 @@
     </row>
     <row r="13" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13" s="4">
-        <v>63994501</v>
+        <v>80160964</v>
       </c>
       <c r="C13" s="4">
-        <v>64034128</v>
+        <v>80183873</v>
       </c>
       <c r="D13" s="4">
-        <v>1317</v>
+        <v>640</v>
       </c>
       <c r="E13" s="4">
-        <v>1293.8785130000001</v>
+        <v>1191.1170669999999</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G13" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H13" s="4">
-        <v>63999374</v>
+        <v>80165838</v>
       </c>
       <c r="I13" s="4">
-        <v>64076061</v>
+        <v>80178577</v>
       </c>
       <c r="J13" s="4">
-        <v>1294</v>
+        <v>42</v>
       </c>
       <c r="K13" s="4">
-        <v>3430.8111159999999</v>
+        <v>1700.847135</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M13" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N13" s="4">
-        <v>63985680</v>
+        <v>80161669</v>
       </c>
       <c r="O13" s="4">
-        <v>64044018</v>
+        <v>80189103</v>
       </c>
       <c r="P13" s="4">
-        <v>1458</v>
+        <v>615</v>
       </c>
       <c r="Q13" s="4">
-        <v>2731.3774370000001</v>
+        <v>1834.9834739999999</v>
       </c>
       <c r="R13" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S13" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" s="4">
-        <v>64009875</v>
+        <v>80175492</v>
       </c>
       <c r="U13" s="4">
-        <v>64015548</v>
+        <v>80180787</v>
       </c>
       <c r="V13" s="4" t="s">
         <v>26</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Z13" s="4" t="s">
         <v>288</v>
@@ -17794,334 +17681,334 @@
     </row>
     <row r="14" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B14" s="4">
-        <v>17976371</v>
+        <v>63052282</v>
       </c>
       <c r="C14" s="4">
-        <v>18074711</v>
+        <v>63092572</v>
       </c>
       <c r="D14" s="4">
-        <v>3913</v>
+        <v>825</v>
       </c>
       <c r="E14" s="4">
-        <v>2870.176172</v>
+        <v>1521.3566880000001</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G14" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H14" s="4">
-        <v>17962052</v>
+        <v>63062915</v>
       </c>
       <c r="I14" s="4">
-        <v>18060780</v>
+        <v>63086509</v>
       </c>
       <c r="J14" s="4">
-        <v>2429</v>
+        <v>423</v>
       </c>
       <c r="K14" s="4">
-        <v>3450.7886920000001</v>
+        <v>1814.0876330000001</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M14" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N14" s="4">
-        <v>17997545</v>
+        <v>63059302</v>
       </c>
       <c r="O14" s="4">
-        <v>18052601</v>
+        <v>63084877</v>
       </c>
       <c r="P14" s="4">
-        <v>882</v>
+        <v>541</v>
       </c>
       <c r="Q14" s="4">
-        <v>1867.4453060000001</v>
+        <v>1370.5586989999999</v>
       </c>
       <c r="R14" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S14" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" s="4">
-        <v>18061046</v>
+        <v>63085267</v>
       </c>
       <c r="U14" s="4">
-        <v>18065942</v>
+        <v>63097361</v>
       </c>
       <c r="V14" s="4" t="s">
         <v>26</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="4">
-        <v>40749771</v>
+        <v>63994501</v>
       </c>
       <c r="C15" s="4">
-        <v>40779522</v>
+        <v>64034128</v>
       </c>
       <c r="D15" s="4">
-        <v>793</v>
+        <v>1317</v>
       </c>
       <c r="E15" s="4">
-        <v>1277.745809</v>
+        <v>1293.8785130000001</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G15" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15" s="4">
-        <v>40757023</v>
+        <v>63999374</v>
       </c>
       <c r="I15" s="4">
-        <v>40776665</v>
+        <v>64076061</v>
       </c>
       <c r="J15" s="4">
-        <v>385</v>
+        <v>1294</v>
       </c>
       <c r="K15" s="4">
-        <v>1800.2435310000001</v>
+        <v>3430.8111159999999</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M15" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N15" s="4">
-        <v>40759889</v>
+        <v>63985680</v>
       </c>
       <c r="O15" s="4">
-        <v>40770830</v>
+        <v>64044018</v>
       </c>
       <c r="P15" s="4">
-        <v>45</v>
+        <v>1458</v>
       </c>
       <c r="Q15" s="4">
-        <v>1139.2922329999999</v>
+        <v>2731.3774370000001</v>
       </c>
       <c r="R15" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S15" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" s="4">
-        <v>40744456</v>
+        <v>64009875</v>
       </c>
       <c r="U15" s="4">
-        <v>40752372</v>
+        <v>64015548</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="AA15" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B16" s="4">
-        <v>56227592</v>
+        <v>17976371</v>
       </c>
       <c r="C16" s="4">
-        <v>56261449</v>
+        <v>18074711</v>
       </c>
       <c r="D16" s="4">
-        <v>587</v>
+        <v>3913</v>
       </c>
       <c r="E16" s="4">
-        <v>1454.591242</v>
+        <v>2870.176172</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G16" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H16" s="4">
-        <v>56233983</v>
+        <v>17962052</v>
       </c>
       <c r="I16" s="4">
-        <v>56244499</v>
+        <v>18060780</v>
       </c>
       <c r="J16" s="4">
-        <v>3</v>
+        <v>2429</v>
       </c>
       <c r="K16" s="4">
-        <v>1693.8803969999999</v>
+        <v>3450.7886920000001</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M16" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N16" s="4">
-        <v>56220525</v>
+        <v>17997545</v>
       </c>
       <c r="O16" s="4">
-        <v>56255193</v>
+        <v>18052601</v>
       </c>
       <c r="P16" s="4">
-        <v>554</v>
+        <v>882</v>
       </c>
       <c r="Q16" s="4">
-        <v>2029.2391689999999</v>
+        <v>1867.4453060000001</v>
       </c>
       <c r="R16" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S16" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T16" s="4">
-        <v>56243786</v>
+        <v>18061046</v>
       </c>
       <c r="U16" s="4">
-        <v>56252025</v>
+        <v>18065942</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>259</v>
+        <v>149</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="AA16" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>4169437</v>
+        <v>40749771</v>
       </c>
       <c r="C17" s="4">
-        <v>4217545</v>
+        <v>40779522</v>
       </c>
       <c r="D17" s="4">
-        <v>723</v>
+        <v>793</v>
       </c>
       <c r="E17" s="4">
-        <v>1810.86626</v>
+        <v>1277.745809</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G17" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H17" s="4">
-        <v>4179846</v>
+        <v>40757023</v>
       </c>
       <c r="I17" s="4">
-        <v>4191340</v>
+        <v>40776665</v>
       </c>
       <c r="J17" s="4">
-        <v>4</v>
+        <v>385</v>
       </c>
       <c r="K17" s="4">
-        <v>1755.0552279999999</v>
+        <v>1800.2435310000001</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>324</v>
       </c>
       <c r="M17" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N17" s="4">
-        <v>4191356</v>
+        <v>40759889</v>
       </c>
       <c r="O17" s="4">
-        <v>4211587</v>
+        <v>40770830</v>
       </c>
       <c r="P17" s="4">
-        <v>477</v>
+        <v>45</v>
       </c>
       <c r="Q17" s="4">
-        <v>1329.908889</v>
+        <v>1139.2922329999999</v>
       </c>
       <c r="R17" s="4" t="s">
         <v>323</v>
       </c>
       <c r="S17" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T17" s="4">
-        <v>4164654</v>
+        <v>40744456</v>
       </c>
       <c r="U17" s="4">
-        <v>4170098</v>
+        <v>40752372</v>
       </c>
       <c r="V17" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -18129,16 +18016,16 @@
         <v>9</v>
       </c>
       <c r="B18" s="4">
-        <v>10887578</v>
+        <v>56227592</v>
       </c>
       <c r="C18" s="4">
-        <v>11044608</v>
+        <v>56261449</v>
       </c>
       <c r="D18" s="4">
-        <v>5371</v>
+        <v>587</v>
       </c>
       <c r="E18" s="4">
-        <v>3689.872711</v>
+        <v>1454.591242</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>322</v>
@@ -18147,16 +18034,16 @@
         <v>9</v>
       </c>
       <c r="H18" s="4">
-        <v>10882047</v>
+        <v>56233983</v>
       </c>
       <c r="I18" s="4">
-        <v>11003407</v>
+        <v>56244499</v>
       </c>
       <c r="J18" s="4">
-        <v>2949</v>
+        <v>3</v>
       </c>
       <c r="K18" s="4">
-        <v>3689.872711</v>
+        <v>1693.8803969999999</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>324</v>
@@ -18165,16 +18052,16 @@
         <v>9</v>
       </c>
       <c r="N18" s="4">
-        <v>10887578</v>
+        <v>56220525</v>
       </c>
       <c r="O18" s="4">
-        <v>11044608</v>
+        <v>56255193</v>
       </c>
       <c r="P18" s="4">
-        <v>5371</v>
+        <v>554</v>
       </c>
       <c r="Q18" s="4">
-        <v>5841.2801280000003</v>
+        <v>2029.2391689999999</v>
       </c>
       <c r="R18" s="4" t="s">
         <v>323</v>
@@ -18183,34 +18070,206 @@
         <v>9</v>
       </c>
       <c r="T18" s="4">
-        <v>10907169</v>
+        <v>56243786</v>
       </c>
       <c r="U18" s="4">
-        <v>10913953</v>
+        <v>56252025</v>
       </c>
       <c r="V18" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W18" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="Z18" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA18" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>9</v>
+      </c>
+      <c r="B19" s="4">
+        <v>4169437</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4217545</v>
+      </c>
+      <c r="D19" s="4">
+        <v>723</v>
+      </c>
+      <c r="E19" s="4">
+        <v>1810.86626</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="G19" s="4">
+        <v>9</v>
+      </c>
+      <c r="H19" s="4">
+        <v>4179846</v>
+      </c>
+      <c r="I19" s="4">
+        <v>4191340</v>
+      </c>
+      <c r="J19" s="4">
+        <v>4</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1755.0552279999999</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="M19" s="4">
+        <v>9</v>
+      </c>
+      <c r="N19" s="4">
+        <v>4191356</v>
+      </c>
+      <c r="O19" s="4">
+        <v>4211587</v>
+      </c>
+      <c r="P19" s="4">
+        <v>477</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>1329.908889</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="S19" s="4">
+        <v>9</v>
+      </c>
+      <c r="T19" s="4">
+        <v>4164654</v>
+      </c>
+      <c r="U19" s="4">
+        <v>4170098</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y19" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="Z19" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="AA19" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
+        <v>9</v>
+      </c>
+      <c r="B20" s="4">
+        <v>10887578</v>
+      </c>
+      <c r="C20" s="4">
+        <v>11044608</v>
+      </c>
+      <c r="D20" s="4">
+        <v>5371</v>
+      </c>
+      <c r="E20" s="4">
+        <v>3689.872711</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="G20" s="4">
+        <v>9</v>
+      </c>
+      <c r="H20" s="4">
+        <v>10882047</v>
+      </c>
+      <c r="I20" s="4">
+        <v>11003407</v>
+      </c>
+      <c r="J20" s="4">
+        <v>2949</v>
+      </c>
+      <c r="K20" s="4">
+        <v>3689.872711</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="M20" s="4">
+        <v>9</v>
+      </c>
+      <c r="N20" s="4">
+        <v>10887578</v>
+      </c>
+      <c r="O20" s="4">
+        <v>11044608</v>
+      </c>
+      <c r="P20" s="4">
+        <v>5371</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>5841.2801280000003</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="S20" s="4">
+        <v>9</v>
+      </c>
+      <c r="T20" s="4">
+        <v>10907169</v>
+      </c>
+      <c r="U20" s="4">
+        <v>10913953</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W20" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="X18" s="4" t="s">
+      <c r="X20" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="Y18" s="4" t="s">
+      <c r="Y20" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="Z18" s="4" t="s">
+      <c r="Z20" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="AA18" s="4" t="s">
+      <c r="AA20" s="4" t="s">
         <v>330</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z19">
-    <sortCondition ref="S2:S19"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:Z21">
+    <sortCondition ref="S4:S21"/>
   </sortState>
+  <mergeCells count="4">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="S2:X2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>